--- a/slot-project/docs/game_spec.xlsx
+++ b/slot-project/docs/game_spec.xlsx
@@ -407,7 +407,7 @@
     <t xml:space="preserve">Message bar</t>
   </si>
   <si>
-    <t xml:space="preserve">(0, -300) 1164x56</t>
+    <t xml:space="preserve">(0, -318) 1164x56</t>
   </si>
   <si>
     <t xml:space="preserve">Idle: GOOD LUCK / on a win: line details / FS: messages</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">→ S1</t>
   </si>
   <si>
-    <t xml:space="preserve">Auto play stop conditions: AUTO pressed again / insufficient balance / BIG WIN or above / free spins triggered (auto continues after FS ends)</t>
+    <t xml:space="preserve">Auto play stop conditions: AUTO pressed again / insufficient balance / BIG WIN or above in the base game. When free spins trigger, the FS play automatically and auto play resumes after they end.</t>
   </si>
   <si>
     <t xml:space="preserve">Control</t>
